--- a/sequences/fastseq_conditions_18.xlsx
+++ b/sequences/fastseq_conditions_18.xlsx
@@ -544,35 +544,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
     </row>
@@ -632,27 +632,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>9</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
     </row>
@@ -728,27 +728,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -808,27 +808,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -840,11 +840,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -904,19 +904,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
     </row>
@@ -984,19 +984,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1016,11 +1016,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
     </row>
@@ -1080,19 +1080,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1256,36 +1256,36 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
     </row>
@@ -1336,44 +1336,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_33.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_33.jpg</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
     </row>
@@ -1432,36 +1432,36 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
     </row>
@@ -1512,19 +1512,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1536,19 +1536,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
     </row>
@@ -1608,36 +1608,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_16.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>9</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -1688,27 +1688,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1720,11 +1720,11 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1776,35 +1776,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>7</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>8</v>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1952,19 +1952,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>10</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1976,19 +1976,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
     </row>
@@ -2040,19 +2040,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2072,11 +2072,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
     </row>
@@ -2128,44 +2128,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_23.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
     </row>
@@ -2216,44 +2216,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_37.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_33.jpg</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="M21" t="n">
         <v>9</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_26.jpg</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
     </row>
@@ -2304,43 +2304,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="I22" t="n">
         <v>10</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_38.jpg</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
     </row>
@@ -2392,19 +2392,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2416,11 +2416,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
     </row>
@@ -2488,69 +2488,69 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_16.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>9</v>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_38.jpg</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
     </row>
@@ -2568,77 +2568,77 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_26.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="M25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_37.jpg</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_26.jpg</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>10</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
     </row>
@@ -2656,35 +2656,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_23.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="K26" t="n">
         <v>3</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_19.jpg</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>7</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
     </row>
@@ -2744,27 +2744,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2776,11 +2776,11 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
     </row>
@@ -2832,11 +2832,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2848,28 +2848,28 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="M28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>9</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_00.png</t>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -2920,44 +2920,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="I29" t="n">
         <v>7</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="M29" t="n">
         <v>9</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_37.jpg</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_04.png</t>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
     </row>
@@ -3008,77 +3008,77 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_16.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_19.jpg</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>9</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>7</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
     </row>
@@ -3096,43 +3096,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_33.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_37.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>7</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_26.jpg</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>8</v>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
     </row>
@@ -3184,44 +3184,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>10</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>5</v>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>9</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
     </row>
@@ -3272,27 +3272,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>9</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3304,11 +3304,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
     </row>
@@ -3360,77 +3360,77 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>stimuli/house/house_06.jpg</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>9</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
     </row>
@@ -3448,27 +3448,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>7</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>8</v>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3536,11 +3536,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
     </row>
@@ -3624,27 +3624,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="I37" t="n">
         <v>7</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>9</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3656,11 +3656,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_37.jpg</t>
+          <t>stimuli/bread/bread_26.jpg</t>
         </is>
       </c>
     </row>
@@ -3720,35 +3720,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
     </row>
@@ -3800,35 +3800,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
     </row>
@@ -3896,35 +3896,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>3</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>7</v>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -3976,27 +3976,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4008,11 +4008,11 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
     </row>
@@ -4072,35 +4072,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -4152,27 +4152,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_33.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>10</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_33.jpg</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
     </row>
@@ -4240,11 +4240,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>7</v>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -4328,35 +4328,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="I45" t="n">
         <v>7</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="K45" t="n">
         <v>9</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>2</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4416,44 +4416,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>3</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>7</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
-        <v>8</v>
-      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
     </row>
@@ -4504,35 +4504,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="I47" t="n">
         <v>7</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>9</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>8</v>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
     </row>
@@ -4608,27 +4608,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4680,27 +4680,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4712,11 +4712,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
     </row>
@@ -4768,11 +4768,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4784,27 +4784,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -4856,35 +4856,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>8</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="I51" t="n">
         <v>7</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>9</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>8</v>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
     </row>
@@ -4952,19 +4952,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4976,11 +4976,11 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
     </row>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_33.jpg</t>
+          <t>stimuli/jacket/jacket_26.jpg</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5136,28 +5136,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="M54" t="n">
         <v>3</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>9</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
     </row>
@@ -5208,77 +5208,77 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_36.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="I55" t="n">
         <v>7</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="M55" t="n">
         <v>9</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_37.jpg</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_03.jpg</t>
         </is>
       </c>
     </row>
@@ -5296,19 +5296,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_23.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5320,19 +5320,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
     </row>
@@ -5384,19 +5384,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>7</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>8</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5416,11 +5416,11 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_36.jpg</t>
+          <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
     </row>
@@ -5472,43 +5472,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_19.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_16.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>7</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_38.jpg</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="K58" t="n">
         <v>3</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_19.jpg</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>7</v>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
     </row>
@@ -5560,35 +5560,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_26.jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_33.jpg</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_37.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_37.jpg</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="K59" t="n">
         <v>7</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>10</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_26.jpg</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_36.jpg</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>8</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_26.jpg</t>
+          <t>stimuli/dog/dog_33.jpg</t>
         </is>
       </c>
     </row>
@@ -5656,11 +5656,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/jacket/jacket_23.jpg</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5672,19 +5672,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_38.jpg</t>
+          <t>stimuli/chair/chair_19.jpg</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/hammer/hammer_16.jpg</t>
         </is>
       </c>
     </row>
@@ -5736,19 +5736,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_26.jpg</t>
+          <t>stimuli/chair/chair_37.jpg</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_03.jpg</t>
+          <t>stimuli/hand/hand_36.jpg</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -5768,11 +5768,11 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
     </row>
